--- a/business_forms/048_professional_services_application_form--business_forms.xlsx
+++ b/business_forms/048_professional_services_application_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'consultant'}</t>
+          <t>consultant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Consultant'}</t>
+          <t>Consultant</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'contractor'}</t>
+          <t>contractor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Contractor'}</t>
+          <t>Contractor</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'full_time'}</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Full Time'}</t>
+          <t>Full Time</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'part_time'}</t>
+          <t>part_time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Part Time'}</t>
+          <t>Part Time</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'project_based'}</t>
+          <t>project_based</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Project Based'}</t>
+          <t>Project Based</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'fixed'}</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Fixed'}</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'hourly'}</t>
+          <t>hourly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Hourly'}</t>
+          <t>Hourly</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'project_based'}</t>
+          <t>project_based</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Project Based'}</t>
+          <t>Project Based</t>
         </is>
       </c>
     </row>
